--- a/test_data/business_scenarios.xlsx
+++ b/test_data/business_scenarios.xlsx
@@ -1,20 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10917"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/rishabhbhangale/Downloads/semantics/test_playwright combined/test_data/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6F88092F-A85B-EB48-8B67-FA16EA97250E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="18980" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="124519"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="124" uniqueCount="83">
   <si>
     <t>Test ID</t>
   </si>
@@ -64,6 +70,21 @@
     <t>SQL File Name</t>
   </si>
   <si>
+    <t>Visual Type</t>
+  </si>
+  <si>
+    <t>Table Visual Name</t>
+  </si>
+  <si>
+    <t>Join Keys</t>
+  </si>
+  <si>
+    <t>Compare Columns</t>
+  </si>
+  <si>
+    <t>DAX Query</t>
+  </si>
+  <si>
     <t>TC-BIZ-001</t>
   </si>
   <si>
@@ -79,6 +100,24 @@
     <t>TC-BIZ-007</t>
   </si>
   <si>
+    <t>TC-BIZ-008</t>
+  </si>
+  <si>
+    <t>TC-BIZ-009</t>
+  </si>
+  <si>
+    <t>TC-BIZ-010</t>
+  </si>
+  <si>
+    <t>TC-BIZ-011</t>
+  </si>
+  <si>
+    <t>TC-BIZ-012</t>
+  </si>
+  <si>
+    <t>TC-BIZ-013</t>
+  </si>
+  <si>
     <t>State-Level Sales Validation</t>
   </si>
   <si>
@@ -94,6 +133,24 @@
     <t>Chairs Orders - Second Class Shipping</t>
   </si>
   <si>
+    <t>California Technology Sales — KPI with Tier 2 DAX Fallback</t>
+  </si>
+  <si>
+    <t>Regional Sales Breakdown — Table Validation (Auto Schema)</t>
+  </si>
+  <si>
+    <t>Category Performance Table — Multi-Metric Row Comparison</t>
+  </si>
+  <si>
+    <t>State &amp; Sub-Category Matrix — Composite Key Validation</t>
+  </si>
+  <si>
+    <t>Ship Mode Order Summary — Full Table + Tier 2 DAX Override</t>
+  </si>
+  <si>
+    <t>All-States Sales Table — Virtual Scroll &amp; Tier 2 DAX Validation</t>
+  </si>
+  <si>
     <t>State</t>
   </si>
   <si>
@@ -103,6 +160,9 @@
     <t>Customer Segment</t>
   </si>
   <si>
+    <t>Region</t>
+  </si>
+  <si>
     <t>California</t>
   </si>
   <si>
@@ -118,15 +178,33 @@
     <t>Second Class</t>
   </si>
   <si>
+    <t>West</t>
+  </si>
+  <si>
     <t>Sub-Category</t>
   </si>
   <si>
+    <t>Category</t>
+  </si>
+  <si>
     <t>Phones</t>
   </si>
   <si>
     <t>Chairs</t>
   </si>
   <si>
+    <t>Technology</t>
+  </si>
+  <si>
+    <t>Consumer</t>
+  </si>
+  <si>
+    <t>Corporate</t>
+  </si>
+  <si>
+    <t>Office Supplies</t>
+  </si>
+  <si>
     <t>Total Sales</t>
   </si>
   <si>
@@ -134,13 +212,70 @@
   </si>
   <si>
     <t># of Orders</t>
+  </si>
+  <si>
+    <t>KPI</t>
+  </si>
+  <si>
+    <t>Table</t>
+  </si>
+  <si>
+    <t>Matrix</t>
+  </si>
+  <si>
+    <t>Sales by Region</t>
+  </si>
+  <si>
+    <t>Sales by Category</t>
+  </si>
+  <si>
+    <t>Sales by State and Sub-Category</t>
+  </si>
+  <si>
+    <t>Orders by Ship Mode</t>
+  </si>
+  <si>
+    <t>Sales by State</t>
+  </si>
+  <si>
+    <t>category</t>
+  </si>
+  <si>
+    <t>state, sub_category</t>
+  </si>
+  <si>
+    <t>ship_mode</t>
+  </si>
+  <si>
+    <t>state</t>
+  </si>
+  <si>
+    <t>total_sales, total_profit, total_quantity</t>
+  </si>
+  <si>
+    <t>total_sales, total_profit</t>
+  </si>
+  <si>
+    <t>order_count, total_sales</t>
+  </si>
+  <si>
+    <t>total_sales</t>
+  </si>
+  <si>
+    <t>EVALUATE ROW("Total Sales", CALCULATE(SUM('SALES'[Sales]), 'SALES'[State] = "California", 'SALES'[Category] = "Technology"))</t>
+  </si>
+  <si>
+    <t>EVALUATE SUMMARIZECOLUMNS('SALES'[Ship_Mode], FILTER(ALL('SALES'), 'SALES'[State] = "California" &amp;&amp; 'SALES'[Segment] = "Corporate" &amp;&amp; 'SALES'[Category] = "Office Supplies"), "order_count", DISTINCTCOUNT('SALES'[Order_ID]), "total_sales", SUM('SALES'[Sales]))</t>
+  </si>
+  <si>
+    <t>EVALUATE SUMMARIZECOLUMNS('SALES'[State], "total_sales", SUM('SALES'[Sales]))</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -203,13 +338,21 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -247,7 +390,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -281,6 +424,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -315,9 +459,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -490,11 +635,34 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P6"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:U12"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="9.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="49.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.83203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.33203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="15.83203125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.33203125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.83203125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="12.33203125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="11.83203125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11.6640625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="11.83203125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="11.6640625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="11.83203125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="11.6640625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="10.1640625" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="12.33203125" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="10" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="26" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="16.33203125" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="31.6640625" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="212.83203125" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:16">
+    <row r="1" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -543,132 +711,351 @@
       <c r="P1" s="1" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="2" spans="1:16">
+      <c r="Q1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="R1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="S1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="T1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="U1" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="2" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="B2" t="s">
-        <v>21</v>
+        <v>32</v>
       </c>
       <c r="C2" t="s">
+        <v>43</v>
+      </c>
+      <c r="D2" t="s">
+        <v>47</v>
+      </c>
+      <c r="E2" t="s">
+        <v>44</v>
+      </c>
+      <c r="F2" t="s">
+        <v>48</v>
+      </c>
+      <c r="G2" t="s">
+        <v>53</v>
+      </c>
+      <c r="H2" t="s">
+        <v>55</v>
+      </c>
+      <c r="O2" t="s">
+        <v>61</v>
+      </c>
+      <c r="Q2" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="3" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
+        <v>22</v>
+      </c>
+      <c r="B3" t="s">
+        <v>33</v>
+      </c>
+      <c r="C3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D3" t="s">
+        <v>48</v>
+      </c>
+      <c r="O3" t="s">
+        <v>61</v>
+      </c>
+      <c r="Q3" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="4" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
+        <v>23</v>
+      </c>
+      <c r="B4" t="s">
+        <v>34</v>
+      </c>
+      <c r="C4" t="s">
+        <v>43</v>
+      </c>
+      <c r="D4" t="s">
+        <v>49</v>
+      </c>
+      <c r="E4" t="s">
+        <v>53</v>
+      </c>
+      <c r="F4" t="s">
+        <v>55</v>
+      </c>
+      <c r="O4" t="s">
+        <v>61</v>
+      </c>
+      <c r="Q4" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="5" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A5" t="s">
+        <v>24</v>
+      </c>
+      <c r="B5" t="s">
+        <v>35</v>
+      </c>
+      <c r="C5" t="s">
+        <v>45</v>
+      </c>
+      <c r="D5" t="s">
+        <v>50</v>
+      </c>
+      <c r="E5" t="s">
+        <v>43</v>
+      </c>
+      <c r="F5" t="s">
+        <v>49</v>
+      </c>
+      <c r="G5" t="s">
+        <v>44</v>
+      </c>
+      <c r="H5" t="s">
+        <v>48</v>
+      </c>
+      <c r="I5" t="s">
+        <v>53</v>
+      </c>
+      <c r="J5" t="s">
+        <v>55</v>
+      </c>
+      <c r="O5" t="s">
+        <v>62</v>
+      </c>
+      <c r="Q5" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="6" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A6" t="s">
+        <v>25</v>
+      </c>
+      <c r="B6" t="s">
+        <v>36</v>
+      </c>
+      <c r="C6" t="s">
+        <v>44</v>
+      </c>
+      <c r="D6" t="s">
+        <v>51</v>
+      </c>
+      <c r="E6" t="s">
+        <v>53</v>
+      </c>
+      <c r="F6" t="s">
+        <v>56</v>
+      </c>
+      <c r="O6" t="s">
+        <v>63</v>
+      </c>
+      <c r="Q6" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="7" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A7" t="s">
         <v>26</v>
       </c>
-      <c r="D2" t="s">
+      <c r="B7" t="s">
+        <v>37</v>
+      </c>
+      <c r="C7" t="s">
+        <v>43</v>
+      </c>
+      <c r="D7" t="s">
+        <v>47</v>
+      </c>
+      <c r="E7" t="s">
+        <v>54</v>
+      </c>
+      <c r="F7" t="s">
+        <v>57</v>
+      </c>
+      <c r="O7" t="s">
+        <v>61</v>
+      </c>
+      <c r="Q7" t="s">
+        <v>64</v>
+      </c>
+      <c r="U7" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="8" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A8" t="s">
+        <v>27</v>
+      </c>
+      <c r="B8" t="s">
+        <v>38</v>
+      </c>
+      <c r="C8" t="s">
+        <v>44</v>
+      </c>
+      <c r="D8" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q8" t="s">
+        <v>65</v>
+      </c>
+      <c r="R8" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="9" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A9" t="s">
+        <v>28</v>
+      </c>
+      <c r="B9" t="s">
+        <v>39</v>
+      </c>
+      <c r="C9" t="s">
+        <v>43</v>
+      </c>
+      <c r="D9" t="s">
+        <v>49</v>
+      </c>
+      <c r="E9" t="s">
+        <v>45</v>
+      </c>
+      <c r="F9" t="s">
+        <v>58</v>
+      </c>
+      <c r="Q9" t="s">
+        <v>65</v>
+      </c>
+      <c r="R9" t="s">
+        <v>68</v>
+      </c>
+      <c r="S9" t="s">
+        <v>72</v>
+      </c>
+      <c r="T9" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="10" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A10" t="s">
         <v>29</v>
       </c>
-      <c r="E2" t="s">
-        <v>27</v>
-      </c>
-      <c r="F2" t="s">
+      <c r="B10" t="s">
+        <v>40</v>
+      </c>
+      <c r="C10" t="s">
+        <v>46</v>
+      </c>
+      <c r="D10" t="s">
+        <v>52</v>
+      </c>
+      <c r="E10" t="s">
+        <v>54</v>
+      </c>
+      <c r="F10" t="s">
+        <v>57</v>
+      </c>
+      <c r="G10" t="s">
+        <v>44</v>
+      </c>
+      <c r="H10" t="s">
+        <v>51</v>
+      </c>
+      <c r="Q10" t="s">
+        <v>66</v>
+      </c>
+      <c r="R10" t="s">
+        <v>69</v>
+      </c>
+      <c r="S10" t="s">
+        <v>73</v>
+      </c>
+      <c r="T10" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="11" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A11" t="s">
         <v>30</v>
       </c>
-      <c r="G2" t="s">
-        <v>34</v>
-      </c>
-      <c r="H2" t="s">
-        <v>35</v>
-      </c>
-      <c r="O2" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="3" spans="1:16">
-      <c r="A3" t="s">
-        <v>17</v>
-      </c>
-      <c r="B3" t="s">
-        <v>22</v>
-      </c>
-      <c r="C3" t="s">
-        <v>27</v>
-      </c>
-      <c r="D3" t="s">
-        <v>30</v>
-      </c>
-      <c r="O3" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="4" spans="1:16">
-      <c r="A4" t="s">
-        <v>18</v>
-      </c>
-      <c r="B4" t="s">
-        <v>23</v>
-      </c>
-      <c r="C4" t="s">
-        <v>26</v>
-      </c>
-      <c r="D4" t="s">
+      <c r="B11" t="s">
+        <v>41</v>
+      </c>
+      <c r="C11" t="s">
+        <v>43</v>
+      </c>
+      <c r="D11" t="s">
+        <v>47</v>
+      </c>
+      <c r="E11" t="s">
+        <v>45</v>
+      </c>
+      <c r="F11" t="s">
+        <v>59</v>
+      </c>
+      <c r="G11" t="s">
+        <v>54</v>
+      </c>
+      <c r="H11" t="s">
+        <v>60</v>
+      </c>
+      <c r="O11" t="s">
+        <v>63</v>
+      </c>
+      <c r="Q11" t="s">
+        <v>65</v>
+      </c>
+      <c r="R11" t="s">
+        <v>70</v>
+      </c>
+      <c r="S11" t="s">
+        <v>74</v>
+      </c>
+      <c r="T11" t="s">
+        <v>78</v>
+      </c>
+      <c r="U11" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="12" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A12" t="s">
         <v>31</v>
       </c>
-      <c r="E4" t="s">
-        <v>34</v>
-      </c>
-      <c r="F4" t="s">
-        <v>35</v>
-      </c>
-      <c r="O4" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="5" spans="1:16">
-      <c r="A5" t="s">
-        <v>19</v>
-      </c>
-      <c r="B5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C5" t="s">
-        <v>28</v>
-      </c>
-      <c r="D5" t="s">
-        <v>32</v>
-      </c>
-      <c r="E5" t="s">
-        <v>26</v>
-      </c>
-      <c r="F5" t="s">
-        <v>31</v>
-      </c>
-      <c r="G5" t="s">
-        <v>27</v>
-      </c>
-      <c r="H5" t="s">
-        <v>30</v>
-      </c>
-      <c r="I5" t="s">
-        <v>34</v>
-      </c>
-      <c r="J5" t="s">
-        <v>35</v>
-      </c>
-      <c r="O5" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="6" spans="1:16">
-      <c r="A6" t="s">
-        <v>20</v>
-      </c>
-      <c r="B6" t="s">
-        <v>25</v>
-      </c>
-      <c r="C6" t="s">
-        <v>27</v>
-      </c>
-      <c r="D6" t="s">
-        <v>33</v>
-      </c>
-      <c r="E6" t="s">
-        <v>34</v>
-      </c>
-      <c r="F6" t="s">
-        <v>36</v>
-      </c>
-      <c r="O6" t="s">
-        <v>39</v>
+      <c r="B12" t="s">
+        <v>42</v>
+      </c>
+      <c r="O12" t="s">
+        <v>61</v>
+      </c>
+      <c r="Q12" t="s">
+        <v>65</v>
+      </c>
+      <c r="R12" t="s">
+        <v>71</v>
+      </c>
+      <c r="S12" t="s">
+        <v>75</v>
+      </c>
+      <c r="T12" t="s">
+        <v>79</v>
+      </c>
+      <c r="U12" t="s">
+        <v>82</v>
       </c>
     </row>
   </sheetData>
